--- a/create_forecast_basic/current/inputs_outputs.xlsx
+++ b/create_forecast_basic/current/inputs_outputs.xlsx
@@ -545,7 +545,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>c:\Users\dpere\Documents\JTMT\forecast_git\create_forecast_basic\current\background_files\TAZ_V4_230518_Published.shp</t>
+          <t>C:\Users\dpere\Documents\JTMT\forecast_git\create_forecast_basic\current\background_files\TAZ_V4_230518_Published.shp</t>
         </is>
       </c>
     </row>
